--- a/config/excel/CfgRoomTemplates.xlsx
+++ b/config/excel/CfgRoomTemplates.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoomTemplates" sheetId="1" r:id="Re01a368e2e3940d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoomTemplates" sheetId="1" r:id="R9a54c1ae9eab4527"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -35,6 +35,11 @@
       <x:sz val="10"/>
       <x:color rgb="FF215E99"/>
       <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="5">
@@ -66,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -123,6 +128,7 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1252,6 +1258,204 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>Mob</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H28" s="14" t="str">
+        <x:v>mob_cover</x:v>
+      </x:c>
+      <x:c r="I28" s="14" t="str"/>
+      <x:c r="J28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>Mob</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H29" s="14" t="str">
+        <x:v>mob_stagger</x:v>
+      </x:c>
+      <x:c r="I29" s="14" t="str"/>
+      <x:c r="J29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>Mob</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G30" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H30" s="14" t="str">
+        <x:v>mob_cover</x:v>
+      </x:c>
+      <x:c r="I30" s="14" t="str"/>
+      <x:c r="J30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>Mob</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G31" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H31" s="14" t="str">
+        <x:v>mob_stagger</x:v>
+      </x:c>
+      <x:c r="I31" s="14" t="str"/>
+      <x:c r="J31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" t="n">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>Mob</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G32" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H32" s="14" t="str">
+        <x:v>mob_cover</x:v>
+      </x:c>
+      <x:c r="I32" s="14" t="str"/>
+      <x:c r="J32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="36" customHeight="1">
+      <x:c r="A33" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>Mob</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H33" s="14" t="str">
+        <x:v>mob_stagger</x:v>
+      </x:c>
+      <x:c r="I33" s="14" t="str"/>
+      <x:c r="J33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
